--- a/e2e/downloadedFile/moju_tunjangan_jabatan_2_Q1.xlsx
+++ b/e2e/downloadedFile/moju_tunjangan_jabatan_2_Q1.xlsx
@@ -95,7 +95,7 @@
     <t>TOTAL</t>
   </si>
   <si>
-    <t>DILI, 14 Agustus 2026</t>
+    <t>DILI, 18 Agustus 2026</t>
   </si>
   <si>
     <t>PREPARED BY</t>
@@ -600,9 +600,7 @@
       <c r="C6" s="3">
         <v>1112342</v>
       </c>
-      <c r="D6" s="4">
-        <v>121.0</v>
-      </c>
+      <c r="D6" s="4"/>
       <c r="E6" s="4"/>
     </row>
     <row r="7" spans="1:5">
@@ -629,7 +627,7 @@
         <v>2123234</v>
       </c>
       <c r="D8" s="4">
-        <v>106.0</v>
+        <v>500.0</v>
       </c>
       <c r="E8" s="4"/>
     </row>
@@ -670,7 +668,7 @@
         <v>110928942</v>
       </c>
       <c r="D11" s="4">
-        <v>106.0</v>
+        <v>100.0</v>
       </c>
       <c r="E11" s="4"/>
     </row>
@@ -711,7 +709,7 @@
         <v>112344</v>
       </c>
       <c r="D14" s="4">
-        <v>106.0</v>
+        <v>100.0</v>
       </c>
       <c r="E14" s="4"/>
     </row>
@@ -812,7 +810,7 @@
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4">
-        <v>439.0</v>
+        <v>700.0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -822,10 +820,10 @@
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="6">
-        <v>439.0</v>
+        <v>700.0</v>
       </c>
       <c r="E23" s="6">
-        <v>439.0</v>
+        <v>700.0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
